--- a/testcases/generated/运营活动/幸运卡片/幸运卡片（集福活动）- 完整用例_20260408.xlsx
+++ b/testcases/generated/运营活动/幸运卡片/幸运卡片（集福活动）- 完整用例_20260408.xlsx
@@ -1903,7 +1903,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="45.0" customHeight="1">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="30.0" customHeight="1">
       <c r="A10" s="3">
         <v>3</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="45.0" customHeight="1">
       <c r="A11" s="3">
         <v>4</v>
       </c>
@@ -2023,7 +2023,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="30.0" customHeight="1">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="30.0" customHeight="1">
       <c r="A13" s="3">
         <v>6</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="30.0" customHeight="1">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="30.0" customHeight="1">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -2143,7 +2143,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="30.0" customHeight="1">
       <c r="A16" s="3">
         <v>9</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="45.0" customHeight="1">
       <c r="A17" s="3">
         <v>10</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="45.0" customHeight="1">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="30.0" customHeight="1">
       <c r="A19" s="3">
         <v>12</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="45.0" customHeight="1">
       <c r="A20" s="3">
         <v>13</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="30.0" customHeight="1">
       <c r="A21" s="3">
         <v>14</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="30.0" customHeight="1">
       <c r="A22" s="3">
         <v>15</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="30.0" customHeight="1">
       <c r="A23" s="3">
         <v>16</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="60.0" customHeight="1">
       <c r="A24" s="3">
         <v>17</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="30.0" customHeight="1">
       <c r="A25" s="3">
         <v>18</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="60.0" customHeight="1">
       <c r="A26" s="3">
         <v>19</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="30.0" customHeight="1">
       <c r="A27" s="3">
         <v>20</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="30.0" customHeight="1">
       <c r="A28" s="3">
         <v>21</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="30.0" customHeight="1">
       <c r="A29" s="3">
         <v>22</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="30.0" customHeight="1">
       <c r="A30" s="3">
         <v>23</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="45.0" customHeight="1">
       <c r="A31" s="3">
         <v>24</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="60.0" customHeight="1">
       <c r="A32" s="3">
         <v>25</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="45.0" customHeight="1">
       <c r="A33" s="3">
         <v>26</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="60.0" customHeight="1">
       <c r="A34" s="3">
         <v>27</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="60.0" customHeight="1">
       <c r="A35" s="3">
         <v>28</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="60.0" customHeight="1">
       <c r="A36" s="3">
         <v>29</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="45.0" customHeight="1">
       <c r="A37" s="3">
         <v>30</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="60.0" customHeight="1">
       <c r="A38" s="3">
         <v>31</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="45.0" customHeight="1">
       <c r="A39" s="3">
         <v>32</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="45.0" customHeight="1">
       <c r="A40" s="3">
         <v>33</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="45.0" customHeight="1">
       <c r="A41" s="3">
         <v>34</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="30.0" customHeight="1">
       <c r="A42" s="3">
         <v>35</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="60.0" customHeight="1">
       <c r="A43" s="3">
         <v>36</v>
       </c>
@@ -2983,7 +2983,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="75.0" customHeight="1">
       <c r="A44" s="3">
         <v>37</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="45.0" customHeight="1">
       <c r="A45" s="3">
         <v>38</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="45.0" customHeight="1">
       <c r="A46" s="3">
         <v>39</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="45.0" customHeight="1">
       <c r="A47" s="3">
         <v>40</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="45.0" customHeight="1">
       <c r="A48" s="3">
         <v>41</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="60.0" customHeight="1">
       <c r="A49" s="3">
         <v>42</v>
       </c>
@@ -3163,7 +3163,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="45.0" customHeight="1">
       <c r="A50" s="3">
         <v>43</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="45.0" customHeight="1">
       <c r="A51" s="3">
         <v>44</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="45.0" customHeight="1">
       <c r="A52" s="3">
         <v>45</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="45.0" customHeight="1">
       <c r="A53" s="3">
         <v>46</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="30.0" customHeight="1">
       <c r="A54" s="3">
         <v>47</v>
       </c>
@@ -3313,7 +3313,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="45.0" customHeight="1">
       <c r="A55" s="3">
         <v>48</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="45.0" customHeight="1">
       <c r="A56" s="3">
         <v>49</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="45.0" customHeight="1">
       <c r="A57" s="3">
         <v>50</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="45.0" customHeight="1">
       <c r="A58" s="3">
         <v>51</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="45.0" customHeight="1">
       <c r="A59" s="3">
         <v>52</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="45.0" customHeight="1">
       <c r="A60" s="3">
         <v>53</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="45.0" customHeight="1">
       <c r="A61" s="3">
         <v>54</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="30.0" customHeight="1">
       <c r="A62" s="3">
         <v>55</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="45.0" customHeight="1">
       <c r="A63" s="3">
         <v>56</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="45.0" customHeight="1">
       <c r="A64" s="3">
         <v>57</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="30.0" customHeight="1">
       <c r="A65" s="3">
         <v>58</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="30.0" customHeight="1">
       <c r="A66" s="3">
         <v>59</v>
       </c>
@@ -3673,7 +3673,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="30.0" customHeight="1">
       <c r="A67" s="3">
         <v>60</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="45.0" customHeight="1">
       <c r="A68" s="3">
         <v>61</v>
       </c>
@@ -3733,7 +3733,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="45.0" customHeight="1">
       <c r="A69" s="3">
         <v>62</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="45.0" customHeight="1">
       <c r="A70" s="3">
         <v>63</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="45.0" customHeight="1">
       <c r="A71" s="3">
         <v>64</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="45.0" customHeight="1">
       <c r="A72" s="3">
         <v>65</v>
       </c>
@@ -3853,7 +3853,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="45.0" customHeight="1">
       <c r="A73" s="3">
         <v>66</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="45.0" customHeight="1">
       <c r="A74" s="3">
         <v>67</v>
       </c>
@@ -3913,7 +3913,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="45.0" customHeight="1">
       <c r="A75" s="3">
         <v>68</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="30.0" customHeight="1">
       <c r="A76" s="3">
         <v>69</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="45.0" customHeight="1">
       <c r="A77" s="3">
         <v>70</v>
       </c>

--- a/testcases/generated/运营活动/幸运卡片/幸运卡片（集福活动）- 完整用例_20260408.xlsx
+++ b/testcases/generated/运营活动/幸运卡片/幸运卡片（集福活动）- 完整用例_20260408.xlsx
@@ -113,10 +113,13 @@
     <t>运营活动权限-幸运卡片配置权限</t>
   </si>
   <si>
-    <t>1、更新版本后；2、账号无锦标赛/幸运卡片权限</t>
-  </si>
-  <si>
-    <t>1、登录后台；2、进入【运营管理&gt;运营活动】；3、尝试访问幸运卡片配置</t>
+    <t>1、更新版本后
+2、账号无锦标赛/幸运卡片权限</t>
+  </si>
+  <si>
+    <t>1、登录后台
+2、进入【运营管理&gt;运营活动】
+3、尝试访问幸运卡片配置</t>
   </si>
   <si>
     <t>1、【运营管理&gt;运营活动】中新增【幸运卡片】菜单
@@ -133,7 +136,8 @@
     <t>1、已启用幸运卡片活动</t>
   </si>
   <si>
-    <t>1、进入活动配置列表页；2、查看显示的字段</t>
+    <t>1、进入活动配置列表页
+2、查看显示的字段</t>
   </si>
   <si>
     <t>显示字段包括：活动名称、活动时间、开奖时间、奖池金额、参与人数、集齐人数、合成卡片数量、实际发放奖励、实际领取奖励、活动状态、操作按钮</t>
@@ -148,7 +152,9 @@
     <t>1、管理员已登录后台</t>
   </si>
   <si>
-    <t>1、进入活动配置页面；2、不填写任何信息；3、点击保存</t>
+    <t>1、进入活动配置页面
+2、不填写任何信息
+3、点击保存</t>
   </si>
   <si>
     <t>1、提示必填项不能为空
@@ -161,7 +167,9 @@
     <t>创建活动配置-完整流程</t>
   </si>
   <si>
-    <t>1、进入活动配置页面；2、填写活动时间、开奖时间、奖池金额；3、点击保存</t>
+    <t>1、进入活动配置页面
+2、填写活动时间、开奖时间、奖池金额
+3、点击保存</t>
   </si>
   <si>
     <t>1、活动配置成功保存
@@ -175,7 +183,9 @@
     <t>活动时间校验-结束时间早于开始时间</t>
   </si>
   <si>
-    <t>1、创建活动配置；2、设置结束时间早于开始时间；3、点击保存</t>
+    <t>1、创建活动配置
+2、设置结束时间早于开始时间
+3、点击保存</t>
   </si>
   <si>
     <t>1、提示结束时间不能早于开始时间
@@ -185,7 +195,9 @@
     <t>活动时间校验-开奖时间早于活动开始时间</t>
   </si>
   <si>
-    <t>1、创建活动配置；2、设置开奖时间早于活动开始时间；3、点击保存</t>
+    <t>1、创建活动配置
+2、设置开奖时间早于活动开始时间
+3、点击保存</t>
   </si>
   <si>
     <t>1、提示开奖时间必须在活动结束之后
@@ -195,7 +207,9 @@
     <t>奖池金额校验-负数验证</t>
   </si>
   <si>
-    <t>1、创建活动配置；2、设置奖池金额为负数；3、点击保存</t>
+    <t>1、创建活动配置
+2、设置奖池金额为负数
+3、点击保存</t>
   </si>
   <si>
     <t>1、提示奖池金额必须大于 0
@@ -205,7 +219,9 @@
     <t>奖池金额校验-小数精度验证</t>
   </si>
   <si>
-    <t>1、创建活动配置；2、设置奖池金额为 1000000.123；3、点击保存</t>
+    <t>1、创建活动配置
+2、设置奖池金额为 1000000.123
+3、点击保存</t>
   </si>
   <si>
     <t>1、提示金额最多保留 2 位小数
@@ -218,10 +234,12 @@
     <t>启用活动</t>
   </si>
   <si>
-    <t>1、活动配置已创建；2、当前时间在活动开始时间之前</t>
-  </si>
-  <si>
-    <t>1、选择活动；2、点击启用按钮</t>
+    <t>1、活动配置已创建
+2、当前时间在活动开始时间之前</t>
+  </si>
+  <si>
+    <t>1、选择活动
+2、点击启用按钮</t>
   </si>
   <si>
     <t>1、活动状态变更为进行中（未开始）
@@ -234,7 +252,8 @@
     <t>1、活动正在进行中</t>
   </si>
   <si>
-    <t>1、选择活动；2、点击关闭按钮</t>
+    <t>1、选择活动
+2、点击关闭按钮</t>
   </si>
   <si>
     <t>1、活动状态变更为已关闭
@@ -245,7 +264,10 @@
     <t>编辑活动配置-进行中活动</t>
   </si>
   <si>
-    <t>1、选择活动；2、点击编辑；3、修改奖池金额；4、保存</t>
+    <t>1、选择活动
+2、点击编辑
+3、修改奖池金额
+4、保存</t>
   </si>
   <si>
     <t>1、允许修改奖池金额
@@ -259,7 +281,8 @@
     <t>1、活动已结束</t>
   </si>
   <si>
-    <t>1、选择活动；2、点击编辑</t>
+    <t>1、选择活动
+2、点击编辑</t>
   </si>
   <si>
     <t>1、不允许编辑已结束的活动
@@ -275,7 +298,8 @@
     <t>1、存在已创建的活动配置</t>
   </si>
   <si>
-    <t>1、选择活动；2、点击复制按钮</t>
+    <t>1、选择活动
+2、点击复制按钮</t>
   </si>
   <si>
     <t>1、创建一个新的活动配置
@@ -289,10 +313,12 @@
     <t>活动数据统计-参与人数</t>
   </si>
   <si>
-    <t>1、活动正在进行中；2、已有用户参与</t>
-  </si>
-  <si>
-    <t>1、进入活动配置列表；2、查看参与人数</t>
+    <t>1、活动正在进行中
+2、已有用户参与</t>
+  </si>
+  <si>
+    <t>1、进入活动配置列表
+2、查看参与人数</t>
   </si>
   <si>
     <t>1、显示参与活动的总用户数
@@ -302,10 +328,12 @@
     <t>活动数据统计-集齐人数</t>
   </si>
   <si>
-    <t>1、活动正在进行中；2、已有用户集齐卡片</t>
-  </si>
-  <si>
-    <t>1、进入活动配置列表；2、查看集齐人数</t>
+    <t>1、活动正在进行中
+2、已有用户集齐卡片</t>
+  </si>
+  <si>
+    <t>1、进入活动配置列表
+2、查看集齐人数</t>
   </si>
   <si>
     <t>1、显示已集齐 5 种卡片的用户数
@@ -315,10 +343,12 @@
     <t>活动数据统计-合成卡片数量</t>
   </si>
   <si>
-    <t>1、活动正在进行中；2、已有用户合成超级卡片</t>
-  </si>
-  <si>
-    <t>1、进入活动配置列表；2、查看合成卡片数量</t>
+    <t>1、活动正在进行中
+2、已有用户合成超级卡片</t>
+  </si>
+  <si>
+    <t>1、进入活动配置列表
+2、查看合成卡片数量</t>
   </si>
   <si>
     <t>1、显示已合成的超级幸运卡片总数
@@ -328,10 +358,15 @@
     <t>手动发放道具给指定用户</t>
   </si>
   <si>
-    <t>1、管理员已登录后台；2、活动进行中</t>
-  </si>
-  <si>
-    <t>1、进入活动管理页面；2、选择手动发放道具；3、输入用户 ID；4、选择道具类型；5、确认发放</t>
+    <t>1、管理员已登录后台
+2、活动进行中</t>
+  </si>
+  <si>
+    <t>1、进入活动管理页面
+2、选择手动发放道具
+3、输入用户 ID
+4、选择道具类型
+5、确认发放</t>
   </si>
   <si>
     <t>1、道具发放到指定用户账户
@@ -343,7 +378,9 @@
     <t>手动发放道具-用户 ID 不存在</t>
   </si>
   <si>
-    <t>1、进入活动管理页面；2、选择不存在的用户 ID；3、发放道具</t>
+    <t>1、进入活动管理页面
+2、选择不存在的用户 ID
+3、发放道具</t>
   </si>
   <si>
     <t>1、提示用户不存在
@@ -353,10 +390,12 @@
     <t>后台查看中奖统计</t>
   </si>
   <si>
-    <t>1、管理员已登录后台；2、活动进行中或已结束</t>
-  </si>
-  <si>
-    <t>1、进入活动统计页面；2、查看中奖人数、预发放人均金额</t>
+    <t>1、管理员已登录后台
+2、活动进行中或已结束</t>
+  </si>
+  <si>
+    <t>1、进入活动统计页面
+2、查看中奖人数、预发放人均金额</t>
   </si>
   <si>
     <t>1、实时显示当前中奖人数
@@ -374,10 +413,12 @@
     <t>侧边栏入口展示-活动未开始</t>
   </si>
   <si>
-    <t>1、活动已启用但未开始；2、用户已登录</t>
-  </si>
-  <si>
-    <t>1、进入大厅页面；2、查看侧边栏</t>
+    <t>1、活动已启用但未开始
+2、用户已登录</t>
+  </si>
+  <si>
+    <t>1、进入大厅页面
+2、查看侧边栏</t>
   </si>
   <si>
     <t>1、侧边栏展示幸运卡片入口及图标
@@ -387,10 +428,13 @@
     <t>侧边栏入口展示-活动进行中</t>
   </si>
   <si>
-    <t>1、活动进行中；2、用户已登录</t>
-  </si>
-  <si>
-    <t>1、进入大厅页面；2、查看侧边栏；3、点击入口</t>
+    <t>1、活动进行中
+2、用户已登录</t>
+  </si>
+  <si>
+    <t>1、进入大厅页面
+2、查看侧边栏
+3、点击入口</t>
   </si>
   <si>
     <t>1、侧边栏展示幸运卡片入口及图标
@@ -400,7 +444,8 @@
     <t>侧边栏入口展示-活动已结束</t>
   </si>
   <si>
-    <t>1、活动已结束；2、用户已登录</t>
+    <t>1、活动已结束
+2、用户已登录</t>
   </si>
   <si>
     <t>1、侧边栏不展示幸运卡片入口
@@ -410,7 +455,8 @@
     <t>头像下拉框入口展示</t>
   </si>
   <si>
-    <t>1、点击头像；2、查看下拉菜单</t>
+    <t>1、点击头像
+2、查看下拉菜单</t>
   </si>
   <si>
     <t>1、下拉框中展示幸运卡片入口
@@ -423,10 +469,13 @@
     <t>活动首页信息展示</t>
   </si>
   <si>
-    <t>1、活动进行中；2、用户已登录并进入活动页面</t>
-  </si>
-  <si>
-    <t>1、查看活动标题、奖池金额、开奖时间；2、查看当前集齐卡片数量；3、查看用户已获得的卡片</t>
+    <t>1、活动进行中
+2、用户已登录并进入活动页面</t>
+  </si>
+  <si>
+    <t>1、查看活动标题、奖池金额、开奖时间
+2、查看当前集齐卡片数量
+3、查看用户已获得的卡片</t>
   </si>
   <si>
     <t>1、标题、奖池金额、开奖时间显示正确
@@ -440,7 +489,8 @@
     <t>1、用户已收集多种卡片</t>
   </si>
   <si>
-    <t>1、进入活动首页；2、查看卡片展示区域</t>
+    <t>1、进入活动首页
+2、查看卡片展示区域</t>
   </si>
   <si>
     <t>1、展示用户已收集的所有卡片
@@ -455,7 +505,8 @@
     <t>1、活动进行中</t>
   </si>
   <si>
-    <t>1、进入活动首页；2、查看开奖倒计时</t>
+    <t>1、进入活动首页
+2、查看开奖倒计时</t>
   </si>
   <si>
     <t>1、显示距离开奖的剩余时间
@@ -466,10 +517,12 @@
     <t>全站滚动播报</t>
   </si>
   <si>
-    <t>1、活动进行中；2、有其他用户获取或合成卡片</t>
-  </si>
-  <si>
-    <t>1、进入活动首页；2、查看滚动播报区域</t>
+    <t>1、活动进行中
+2、有其他用户获取或合成卡片</t>
+  </si>
+  <si>
+    <t>1、进入活动首页
+2、查看滚动播报区域</t>
   </si>
   <si>
     <t>1、滚动展示全站用户获取卡片记录
@@ -499,10 +552,13 @@
     <t>每日登录任务领取卡片</t>
   </si>
   <si>
-    <t>1、活动进行中；2、用户当日未领取登录奖励</t>
-  </si>
-  <si>
-    <t>1、进入活动页面；2、查看每日登录任务状态；3、点击领取</t>
+    <t>1、活动进行中
+2、用户当日未领取登录奖励</t>
+  </si>
+  <si>
+    <t>1、进入活动页面
+2、查看每日登录任务状态
+3、点击领取</t>
   </si>
   <si>
     <t>1、任务显示可领取状态
@@ -514,10 +570,12 @@
     <t>每日登录任务-已领取状态</t>
   </si>
   <si>
-    <t>1、活动进行中；2、用户当日已领取登录奖励</t>
-  </si>
-  <si>
-    <t>1、进入活动页面；2、查看每日登录任务状态</t>
+    <t>1、活动进行中
+2、用户当日已领取登录奖励</t>
+  </si>
+  <si>
+    <t>1、进入活动页面
+2、查看每日登录任务状态</t>
   </si>
   <si>
     <t>1、任务显示已完成状态
@@ -528,10 +586,13 @@
     <t>打码量达标任务卡片发放</t>
   </si>
   <si>
-    <t>1、活动进行中；2、用户当日打码量未达到 1000</t>
-  </si>
-  <si>
-    <t>1、用户进行真金投注；2、打码量累计达到 1000；3、查看任务状态并领取卡片</t>
+    <t>1、活动进行中
+2、用户当日打码量未达到 1000</t>
+  </si>
+  <si>
+    <t>1、用户进行真金投注
+2、打码量累计达到 1000
+3、查看任务状态并领取卡片</t>
   </si>
   <si>
     <t>1、打码量实时累计
@@ -543,10 +604,12 @@
     <t>打码量任务-只记录真金投注</t>
   </si>
   <si>
-    <t>1、活动进行中；2、用户使用 bonus 金投注</t>
-  </si>
-  <si>
-    <t>1、用户使用 bonus 金进行投注；2、查看打码量累计</t>
+    <t>1、活动进行中
+2、用户使用 bonus 金投注</t>
+  </si>
+  <si>
+    <t>1、用户使用 bonus 金进行投注
+2、查看打码量累计</t>
   </si>
   <si>
     <t>1、bonus 金投注不计入打码量
@@ -557,10 +620,12 @@
     <t>邀请下级充值任务卡片发放</t>
   </si>
   <si>
-    <t>1、活动进行中；2、用户有直属下级</t>
-  </si>
-  <si>
-    <t>1、下级用户完成首次充值；2、查看上级用户是否获得卡片奖励</t>
+    <t>1、活动进行中
+2、用户有直属下级</t>
+  </si>
+  <si>
+    <t>1、下级用户完成首次充值
+2、查看上级用户是否获得卡片奖励</t>
   </si>
   <si>
     <t>1、下级充值成功后
@@ -571,10 +636,12 @@
     <t>邀请下级任务-CPF 和 IP 限制</t>
   </si>
   <si>
-    <t>1、活动进行中；2、存在 CPF 和 IP 限制规则</t>
-  </si>
-  <si>
-    <t>1、下级用户充值；2、检查是否符合同 CPF 和 IP 限制规则</t>
+    <t>1、活动进行中
+2、存在 CPF 和 IP 限制规则</t>
+  </si>
+  <si>
+    <t>1、下级用户充值
+2、检查是否符合同 CPF 和 IP 限制规则</t>
   </si>
   <si>
     <t>1、同步 CPF 和 IP 限制规则
@@ -585,10 +652,13 @@
     <t>邀请下级任务-阶梯配置</t>
   </si>
   <si>
-    <t>1、活动进行中；2、后台配置了阶梯奖励</t>
-  </si>
-  <si>
-    <t>1、邀请第 1 个下级充值；2、邀请第 5 个下级充值；3、查看奖励</t>
+    <t>1、活动进行中
+2、后台配置了阶梯奖励</t>
+  </si>
+  <si>
+    <t>1、邀请第 1 个下级充值
+2、邀请第 5 个下级充值
+3、查看奖励</t>
   </si>
   <si>
     <t>1、根据阶梯配置发放不同数量卡片
@@ -598,7 +668,8 @@
     <t>任务列表展示</t>
   </si>
   <si>
-    <t>1、进入活动页面；2、查看任务列表</t>
+    <t>1、进入活动页面
+2、查看任务列表</t>
   </si>
   <si>
     <t>1、显示所有可参与的任务
@@ -616,7 +687,9 @@
     <t>1、用户已集齐 5 种不同卡片</t>
   </si>
   <si>
-    <t>1、进入活动页面；2、查看合成按钮状态；3、点击合成按钮</t>
+    <t>1、进入活动页面
+2、查看合成按钮状态
+3、点击合成按钮</t>
   </si>
   <si>
     <t>1、集齐 5 种不同卡片后合成按钮可点击
@@ -632,7 +705,8 @@
     <t>1、用户未集齐 5 种不同卡片</t>
   </si>
   <si>
-    <t>1、进入活动页面；2、查看合成按钮状态</t>
+    <t>1、进入活动页面
+2、查看合成按钮状态</t>
   </si>
   <si>
     <t>1、合成按钮置灰不可点击
@@ -660,7 +734,9 @@
     <t>1、用户已完成卡片合成</t>
   </si>
   <si>
-    <t>1、合成动画展示完成后；2、查看分享按钮；3、点击分享</t>
+    <t>1、合成动画展示完成后
+2、查看分享按钮
+3、点击分享</t>
   </si>
   <si>
     <t>1、分享按钮展示正常
@@ -688,10 +764,14 @@
     <t>活动开奖自动结算</t>
   </si>
   <si>
-    <t>1、活动已到期；2、到达开奖时间 12:00；3、有用户持有超级幸运卡片</t>
-  </si>
-  <si>
-    <t>1、系统到达开奖时间；2、计算中奖金额：奖池金额/中奖次数；3、发放奖金给中奖用户</t>
+    <t>1、活动已到期
+2、到达开奖时间 12:00
+3、有用户持有超级幸运卡片</t>
+  </si>
+  <si>
+    <t>1、系统到达开奖时间
+2、计算中奖金额：奖池金额/中奖次数
+3、发放奖金给中奖用户</t>
   </si>
   <si>
     <t>1、系统自动触发开奖
@@ -703,7 +783,8 @@
     <t>中奖金额计算-单人多次中奖</t>
   </si>
   <si>
-    <t>1、活动已结束；2、有用户持有多个超级幸运卡片</t>
+    <t>1、活动已结束
+2、有用户持有多个超级幸运卡片</t>
   </si>
   <si>
     <t>1、系统计算中奖金额</t>
@@ -717,7 +798,8 @@
     <t>开奖通知</t>
   </si>
   <si>
-    <t>1、活动已开奖；2、用户持有超级幸运卡片</t>
+    <t>1、活动已开奖
+2、用户持有超级幸运卡片</t>
   </si>
   <si>
     <t>1、系统发送开奖通知</t>
@@ -731,7 +813,8 @@
     <t>无中奖用户情况</t>
   </si>
   <si>
-    <t>1、活动已结束；2、没有用户持有超级幸运卡片</t>
+    <t>1、活动已结束
+2、没有用户持有超级幸运卡片</t>
   </si>
   <si>
     <t>1、系统执行开奖</t>
@@ -748,10 +831,13 @@
     <t>多余卡片兑换免费旋转</t>
   </si>
   <si>
-    <t>1、活动已结束并开奖；2、用户有多余的普通卡片</t>
-  </si>
-  <si>
-    <t>1、进入兑换页面；2、选择兑换免费旋转；3、确认兑换</t>
+    <t>1、活动已结束并开奖
+2、用户有多余的普通卡片</t>
+  </si>
+  <si>
+    <t>1、进入兑换页面
+2、选择兑换免费旋转
+3、确认兑换</t>
   </si>
   <si>
     <t>1、显示可兑换的免费旋转选项
@@ -762,10 +848,13 @@
     <t>兑换次数上限验证</t>
   </si>
   <si>
-    <t>1、活动已结束；2、后台设置了兑换次数上限</t>
-  </si>
-  <si>
-    <t>1、用户多次兑换；2、达到兑换上限；3、继续兑换</t>
+    <t>1、活动已结束
+2、后台设置了兑换次数上限</t>
+  </si>
+  <si>
+    <t>1、用户多次兑换
+2、达到兑换上限
+3、继续兑换</t>
   </si>
   <si>
     <t>1、达到上限后无法继续兑换
@@ -778,10 +867,12 @@
     <t>兑换时间限制</t>
   </si>
   <si>
-    <t>1、活动已结束；2、兑换时间已过期</t>
-  </si>
-  <si>
-    <t>1、进入兑换页面；2、尝试兑换</t>
+    <t>1、活动已结束
+2、兑换时间已过期</t>
+  </si>
+  <si>
+    <t>1、进入兑换页面
+2、尝试兑换</t>
   </si>
   <si>
     <t>1、提示兑换时间已过期
@@ -792,7 +883,8 @@
     <t>兑换比例配置</t>
   </si>
   <si>
-    <t>1、活动已结束；2、后台配置了兑换比例</t>
+    <t>1、活动已结束
+2、后台配置了兑换比例</t>
   </si>
   <si>
     <t>1、查看兑换规则</t>
@@ -812,7 +904,8 @@
     <t>1、用户有道具获取记录</t>
   </si>
   <si>
-    <t>1、进入活动页面；2、点击查看记录</t>
+    <t>1、进入活动页面
+2、点击查看记录</t>
   </si>
   <si>
     <t>1、展示用户所有道具获取记录
@@ -826,7 +919,8 @@
     <t>1、用户有多条道具获取记录</t>
   </si>
   <si>
-    <t>1、进入记录页面；2、使用筛选功能</t>
+    <t>1、进入记录页面
+2、使用筛选功能</t>
   </si>
   <si>
     <t>1、可按获取方式筛选
@@ -840,7 +934,8 @@
     <t>1、用户有合成记录</t>
   </si>
   <si>
-    <t>1、进入活动页面；2、查看合成记录</t>
+    <t>1、进入活动页面
+2、查看合成记录</t>
   </si>
   <si>
     <t>1、展示用户所有合成记录
@@ -851,10 +946,12 @@
     <t>中奖记录展示</t>
   </si>
   <si>
-    <t>1、活动已开奖；2、用户有中奖记录</t>
-  </si>
-  <si>
-    <t>1、进入活动页面；2、查看中奖记录</t>
+    <t>1、活动已开奖
+2、用户有中奖记录</t>
+  </si>
+  <si>
+    <t>1、进入活动页面
+2、查看中奖记录</t>
   </si>
   <si>
     <t>1、展示中奖金额
@@ -868,10 +965,12 @@
     <t>赠送金币报表新增幸运卡片</t>
   </si>
   <si>
-    <t>1、活动进行中或已结束；2、有卡片发放记录</t>
-  </si>
-  <si>
-    <t>1、进入赠送金币报表页面；2、查看幸运卡片相关数据</t>
+    <t>1、活动进行中或已结束
+2、有卡片发放记录</t>
+  </si>
+  <si>
+    <t>1、进入赠送金币报表页面
+2、查看幸运卡片相关数据</t>
   </si>
   <si>
     <t>1、报表新增幸运卡片统计项
@@ -882,10 +981,12 @@
     <t>赠金报表数据导出</t>
   </si>
   <si>
-    <t>1、活动已结束；2、有完整的数据记录</t>
-  </si>
-  <si>
-    <t>1、进入赠金报表页面；2、点击导出按钮</t>
+    <t>1、活动已结束
+2、有完整的数据记录</t>
+  </si>
+  <si>
+    <t>1、进入赠金报表页面
+2、点击导出按钮</t>
   </si>
   <si>
     <t>1、导出包含幸运卡片数据的 Excel 文件
@@ -918,7 +1019,8 @@
     <t>1、用户切换不同语言</t>
   </si>
   <si>
-    <t>1、切换语言；2、查看活动标题</t>
+    <t>1、切换语言
+2、查看活动标题</t>
   </si>
   <si>
     <t>1、活动标题正确翻译为对应语言
@@ -931,7 +1033,8 @@
     <t>多语言切换-任务描述</t>
   </si>
   <si>
-    <t>1、切换语言；2、查看任务描述</t>
+    <t>1、切换语言
+2、查看任务描述</t>
   </si>
   <si>
     <t>1、任务描述正确翻译为对应语言
@@ -941,7 +1044,8 @@
     <t>多语言切换-按钮文本</t>
   </si>
   <si>
-    <t>1、切换语言；2、查看按钮文本</t>
+    <t>1、切换语言
+2、查看按钮文本</t>
   </si>
   <si>
     <t>1、所有按钮文本正确翻译
@@ -970,7 +1074,8 @@
     <t>1、网络正常</t>
   </si>
   <si>
-    <t>1、进入活动页面；2、记录加载时间</t>
+    <t>1、进入活动页面
+2、记录加载时间</t>
   </si>
   <si>
     <t>1、页面在 3 秒内加载完成
@@ -984,7 +1089,8 @@
     <t>并发领取卡片</t>
   </si>
   <si>
-    <t>1、活动进行中；2、用户同时点击多个任务领取</t>
+    <t>1、活动进行中
+2、用户同时点击多个任务领取</t>
   </si>
   <si>
     <t>1、快速点击多个领取按钮</t>
@@ -1015,7 +1121,8 @@
     <t>断网重连后数据同步</t>
   </si>
   <si>
-    <t>1、用户在活动期间断网；2、重新连接网络</t>
+    <t>1、用户在活动期间断网
+2、重新连接网络</t>
   </si>
   <si>
     <t>1、断网后重新打开活动页面</t>
@@ -1029,10 +1136,12 @@
     <t>活动结束自动清空道具</t>
   </si>
   <si>
-    <t>1、活动已结束；2、用户还有未使用的道具</t>
-  </si>
-  <si>
-    <t>1、活动结束时间到达；2、系统执行清空操作</t>
+    <t>1、活动已结束
+2、用户还有未使用的道具</t>
+  </si>
+  <si>
+    <t>1、活动结束时间到达
+2、系统执行清空操作</t>
   </si>
   <si>
     <t>1、未使用的普通卡片被清空
@@ -1046,7 +1155,8 @@
     <t>1、后台配置了卡片权重</t>
   </si>
   <si>
-    <t>1、用户多次领取卡片；2、统计卡片类型分布</t>
+    <t>1、用户多次领取卡片
+2、统计卡片类型分布</t>
   </si>
   <si>
     <t>1、高权重卡片出现频率高
@@ -1088,10 +1198,12 @@
     <t>任务进度实时更新</t>
   </si>
   <si>
-    <t>1、活动进行中；2、用户正在进行任务</t>
-  </si>
-  <si>
-    <t>1、完成打码量任务；2、查看任务进度</t>
+    <t>1、活动进行中
+2、用户正在进行任务</t>
+  </si>
+  <si>
+    <t>1、完成打码量任务
+2、查看任务进度</t>
   </si>
   <si>
     <t>1、任务进度实时更新
@@ -1101,10 +1213,12 @@
     <t>奖金发放失败处理</t>
   </si>
   <si>
-    <t>1、活动已开奖；2、奖金发放过程中出现异常</t>
-  </si>
-  <si>
-    <t>1、系统执行奖金发放；2、模拟发放失败</t>
+    <t>1、活动已开奖
+2、奖金发放过程中出现异常</t>
+  </si>
+  <si>
+    <t>1、系统执行奖金发放
+2、模拟发放失败</t>
   </si>
   <si>
     <t>1、记录发放失败的用户和金额
@@ -1933,7 +2047,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" ht="15.0" customHeight="1">
+    <row r="9" ht="30.0" customHeight="1">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -1963,7 +2077,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" ht="30.0" customHeight="1">
+    <row r="10" ht="45.0" customHeight="1">
       <c r="A10" s="3">
         <v>3</v>
       </c>
@@ -2023,7 +2137,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" ht="30.0" customHeight="1">
+    <row r="12" ht="45.0" customHeight="1">
       <c r="A12" s="3">
         <v>5</v>
       </c>
@@ -2053,7 +2167,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" ht="30.0" customHeight="1">
+    <row r="13" ht="45.0" customHeight="1">
       <c r="A13" s="3">
         <v>6</v>
       </c>
@@ -2083,7 +2197,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" ht="30.0" customHeight="1">
+    <row r="14" ht="45.0" customHeight="1">
       <c r="A14" s="3">
         <v>7</v>
       </c>
@@ -2113,7 +2227,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" ht="30.0" customHeight="1">
+    <row r="15" ht="45.0" customHeight="1">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -2203,7 +2317,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" ht="45.0" customHeight="1">
+    <row r="18" ht="60.0" customHeight="1">
       <c r="A18" s="3">
         <v>11</v>
       </c>
@@ -2383,7 +2497,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" ht="60.0" customHeight="1">
+    <row r="24" ht="75.0" customHeight="1">
       <c r="A24" s="3">
         <v>17</v>
       </c>
@@ -2413,7 +2527,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="25" ht="30.0" customHeight="1">
+    <row r="25" ht="45.0" customHeight="1">
       <c r="A25" s="3">
         <v>18</v>
       </c>
@@ -2503,7 +2617,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="28" ht="30.0" customHeight="1">
+    <row r="28" ht="45.0" customHeight="1">
       <c r="A28" s="3">
         <v>21</v>
       </c>
@@ -2923,7 +3037,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42" ht="30.0" customHeight="1">
+    <row r="42" ht="45.0" customHeight="1">
       <c r="A42" s="3">
         <v>35</v>
       </c>
@@ -3283,7 +3397,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="54" ht="30.0" customHeight="1">
+    <row r="54" ht="45.0" customHeight="1">
       <c r="A54" s="3">
         <v>47</v>
       </c>
